--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#15</t>
+          <t>#16</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,21 +518,21 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#16</t>
+          <t>#17</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>518</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>99.81%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,21 +518,21 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#17</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>518</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>99.81%</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>#19</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,21 +518,21 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#19</t>
+          <t>#20</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>518</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>99.81%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#20</t>
+          <t>#21</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#21</t>
+          <t>#22</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#22</t>
+          <t>#23</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#23</t>
+          <t>#24</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">

--- a/reports/latest/android/Excel/Execution_Summary.xlsx
+++ b/reports/latest/android/Excel/Execution_Summary.xlsx
@@ -518,7 +518,7 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#24</t>
+          <t>#25</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
